--- a/static/excel/WMT_model.xlsx
+++ b/static/excel/WMT_model.xlsx
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>958671.0292390001</v>
+        <v>952931.916068</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $120.27</t>
+          <t>FMP marketCap  |  price $119.55</t>
         </is>
       </c>
     </row>
@@ -7653,25 +7653,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.04969999999999999</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A2CAAEY — AA</t>
         </is>
       </c>
     </row>
@@ -7744,11 +7746,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0598</v>
+        <v>0.0565</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -7809,16 +7811,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8181,13 +8183,13 @@
         <v/>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.052</v>
+        <v>0.0536</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.0476</v>
+        <v>0.0467</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.0497</v>
+        <v>0.0515</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8531,13 +8533,13 @@
         <v/>
       </c>
       <c r="G15" s="77" t="n">
-        <v>750252.1</v>
+        <v>751354.6</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>785929.7</v>
+        <v>786442.4</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>824966.5</v>
+        <v>826959.8</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8565,27 +8567,27 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>743,665 — 755,634</t>
+          <t>744,093 — 756,366</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>776,560 — 797,096</t>
+          <t>770,970 — 798,876</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>823,367 — 826,566</t>
+          <t>825,036 — 828,884</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>842,019 — 862,480</t>
+          <t>845,072 — 869,403</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>878,389 — 899,734</t>
+          <t>877,551 — 902,817</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8606,10 +8608,10 @@
         </is>
       </c>
       <c r="G17" s="84" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H17" s="84" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I17" s="84" t="n">
         <v>16</v>
@@ -8729,13 +8731,13 @@
         <v/>
       </c>
       <c r="G20" s="77" t="n">
-        <v>61189.3</v>
+        <v>61279.2</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>64099.1</v>
+        <v>64140.9</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>67282.89999999999</v>
+        <v>67445.39999999999</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8763,27 +8765,27 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>60,652 — 61,628</t>
+          <t>60,687 — 61,688</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>63,335 — 65,010</t>
+          <t>62,879 — 65,155</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>67,152 — 67,413</t>
+          <t>67,289 — 67,602</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>68,674 — 70,342</t>
+          <t>68,923 — 70,907</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>71,640 — 73,381</t>
+          <t>71,572 — 73,632</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -9963,7 +9965,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>120.27</v>
+        <v>119.55</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10063,7 +10065,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — WMT  |  Master Prompt v2  |  23 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — WMT  |  Master Prompt v2  |  26 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10582,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 43.4x  |  5yr avg 35.0x  |  DCF-implied 16.6x [ref only — not used as benchmark]  [+24% vs benchmark]  [trail=3.16 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=2.83]  PEG≈823.17 (trailing_pe=43.4x / rev_cagr=5%, revenue proxy)</t>
+          <t>Fwd P/E 41.2x (scoring basis)  |  5yr avg 35.0x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.17 | fwd_pe=41.2x→4.17 | abs=1.5 → blended 40/40/20=3.63]  PEG=702.85 (fwd_pe=41.2x / eps_growth=6%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
       <c r="E22" s="131" t="inlineStr">
@@ -10589,7 +10591,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>2.83</v>
+        <v>3.88</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10597,7 +10599,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 43.4x  |  5yr avg 35.0x  |  DCF-implied 16.6x [ref only — not used as benchmark]  [+24% vs benchmark]  [trail=3.16 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=2.83]  PEG≈823.17 (trailing_pe=43.4x / rev_cagr=5%, revenue proxy)</t>
+          <t>Fwd P/E 41.2x (scoring basis)  |  5yr avg 35.0x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.17 | fwd_pe=41.2x→4.17 | abs=1.5 → blended 40/40/20=3.63]  PEG=702.85 (fwd_pe=41.2x / eps_growth=6%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10619,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 24.3x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | no_fwd_data(fallback) | abs=0.0 → blended 40/40/20=0.72]  [fcf_yield=1.6% vs rf=4.6%  spread=-3.0%→modifier=-0.50]</t>
+          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 22.5x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | fwd_pfcf=60.7x→1.70 | abs=0.0 → blended 40/40/20=1.04]  [fcf_yield=1.6% vs rf=4.6%  spread=-3.0%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10626,7 +10628,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10634,7 +10636,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 24.3x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | no_fwd_data(fallback) | abs=0.0 → blended 40/40/20=0.72]  [fcf_yield=1.6% vs rf=4.6%  spread=-3.0%→modifier=-0.50]</t>
+          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 22.5x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | fwd_pfcf=60.7x→1.70 | abs=0.0 → blended 40/40/20=1.04]  [fcf_yield=1.6% vs rf=4.6%  spread=-3.0%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/WMT_model.xlsx
+++ b/static/excel/WMT_model.xlsx
@@ -7353,11 +7353,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>952931.916068</v>
+        <v>947750.772234</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $119.55</t>
+          <t>FMP marketCap  |  price $118.9</t>
         </is>
       </c>
     </row>
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.043</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: None</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.043</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.035</v>
+        <v>1.036</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7665,15 +7665,13 @@
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield  (rating-tier index)</t>
-        </is>
-      </c>
-      <c r="B32" s="46" t="n">
-        <v>0.04969999999999999</v>
-      </c>
+          <t>FRED matched yield</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="n"/>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>FRED BAMLC0A2CAAEY — AA</t>
+          <t>No rating returned — FRED method not applicable</t>
         </is>
       </c>
     </row>
@@ -7716,11 +7714,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0529</v>
+        <v>0.05019999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.72%</t>
+          <t>Rf 4.30% + spread 0.72%</t>
         </is>
       </c>
     </row>
@@ -7746,11 +7744,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0565</v>
+        <v>0.0585</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 3 source(s) above — override freely</t>
+          <t>Default = average of 2 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9963,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>119.55</v>
+        <v>118.9</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10065,7 +10063,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — WMT  |  Master Prompt v2  |  26 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — WMT  |  Master Prompt v2  |  29 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10580,7 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Fwd P/E 41.2x (scoring basis)  |  5yr avg 35.0x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.17 | fwd_pe=41.2x→4.17 | abs=1.5 → blended 40/40/20=3.63]  PEG=702.85 (fwd_pe=41.2x / eps_growth=6%)  [revision:Modest upgrade expected→+0.25]</t>
+          <t>Fwd P/E 41.0x (scoring basis)  |  5yr avg 35.0x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+17% vs benchmark]  [trail=4.26 | fwd_pe=41.0x→4.26 | abs=1.5 → blended 40/40/20=3.71]  PEG=700.84 (fwd_pe=41.0x / eps_growth=6%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
       <c r="E22" s="131" t="inlineStr">
@@ -10591,7 +10589,7 @@
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10599,7 +10597,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Fwd P/E 41.2x (scoring basis)  |  5yr avg 35.0x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+18% vs benchmark]  [trail=4.17 | fwd_pe=41.2x→4.17 | abs=1.5 → blended 40/40/20=3.63]  PEG=702.85 (fwd_pe=41.2x / eps_growth=6%)  [revision:Modest upgrade expected→+0.25]</t>
+          <t>Fwd P/E 41.0x (scoring basis)  |  5yr avg 35.0x  |  DCF-implied 15.3x [ref only — not used as benchmark]  [+17% vs benchmark]  [trail=4.26 | fwd_pe=41.0x→4.26 | abs=1.5 → blended 40/40/20=3.71]  PEG=700.84 (fwd_pe=41.0x / eps_growth=6%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10617,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 22.5x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | fwd_pfcf=60.7x→1.70 | abs=0.0 → blended 40/40/20=1.04]  [fcf_yield=1.6% vs rf=4.6%  spread=-3.0%→modifier=-0.50]</t>
+          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 22.5x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | fwd_pfcf=60.4x→1.79 | abs=0.0 → blended 40/40/20=1.07]  [fcf_yield=1.6% vs rf=4.3%  spread=-2.7%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10628,7 +10626,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10636,7 +10634,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 22.5x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | fwd_pfcf=60.7x→1.70 | abs=0.0 → blended 40/40/20=1.04]  [fcf_yield=1.6% vs rf=4.6%  spread=-3.0%→modifier=-0.50]</t>
+          <t>Current 63.7x  |  5yr avg 44.7x  |  DCF-implied 22.5x [ref only — not used as benchmark]  [+43% vs benchmark]  [trail=0.90 | fwd_pfcf=60.4x→1.79 | abs=0.0 → blended 40/40/20=1.07]  [fcf_yield=1.6% vs rf=4.3%  spread=-2.7%→modifier=-0.50]</t>
         </is>
       </c>
     </row>
